--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/3_five_bus_radial_grid_1ph_dyn_MP_pf_sc_results_0_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/3_five_bus_radial_grid_1ph_dyn_MP_pf_sc_results_0_bus.xlsx
@@ -68,19 +68,19 @@
     <t>pf_va_degree</t>
   </si>
   <si>
-    <t>Bus_0</t>
-  </si>
-  <si>
     <t>Bus_1</t>
-  </si>
-  <si>
-    <t>Bus_2</t>
   </si>
   <si>
     <t>Bus_3</t>
   </si>
   <si>
     <t>Bus_4</t>
+  </si>
+  <si>
+    <t>Bus_0</t>
+  </si>
+  <si>
+    <t>Bus_2</t>
   </si>
   <si>
     <t>pf_ikss_a_ka</t>
@@ -526,22 +526,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>5.248639108480242</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1000.000056712887</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1.324394473835046</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>13.24394453564036</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>84.28940677566904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -595,22 +595,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>5.248639108480242</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1000.000056712887</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1.324394473835046</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>13.24394453564036</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>84.28940677566904</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -707,7 +707,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -825,7 +825,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -943,7 +943,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1071,7 +1071,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1189,7 +1189,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1248,7 +1248,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1307,7 +1307,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1553,7 +1553,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1917,7 +1917,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2281,7 +2281,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2399,7 +2399,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2527,7 +2527,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2704,7 +2704,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2763,7 +2763,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2891,7 +2891,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>5.248639108526413</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3382,7 +3382,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3506,7 +3506,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>5.248639108526413</v>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3764,7 +3764,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3826,7 +3826,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.617960382473001</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4146,7 +4146,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4365,7 +4365,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>5.248639108480242</v>
@@ -4388,7 +4388,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4457,7 +4457,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4552,7 +4552,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.617960382473001</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4676,7 +4676,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>4.198911195792622</v>
@@ -4996,7 +4996,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5058,7 +5058,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5182,7 +5182,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>4.198911195792622</v>
@@ -5378,7 +5378,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5440,7 +5440,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5502,7 +5502,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5564,7 +5564,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.012913138756735</v>
@@ -5760,7 +5760,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5822,7 +5822,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5884,7 +5884,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6080,7 +6080,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.012913138756735</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6204,7 +6204,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6266,7 +6266,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6328,7 +6328,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6462,7 +6462,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6524,7 +6524,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6648,7 +6648,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6710,7 +6710,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6844,7 +6844,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6906,7 +6906,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7030,7 +7030,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7226,7 +7226,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -7288,7 +7288,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7350,7 +7350,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7412,7 +7412,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7474,7 +7474,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7608,7 +7608,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -7670,7 +7670,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7732,7 +7732,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7856,7 +7856,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7990,7 +7990,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -8052,7 +8052,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8176,7 +8176,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8238,7 +8238,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.617960382498489</v>
@@ -8356,7 +8356,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8379,7 +8379,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8425,7 +8425,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8520,7 +8520,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -8582,7 +8582,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8644,7 +8644,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8706,7 +8706,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8768,7 +8768,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8902,7 +8902,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -8964,7 +8964,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9026,7 +9026,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9088,7 +9088,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9150,7 +9150,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9284,7 +9284,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -9346,7 +9346,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9408,7 +9408,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9470,7 +9470,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9532,7 +9532,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9627,7 +9627,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.617960382498489</v>
@@ -9650,7 +9650,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9696,7 +9696,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9719,7 +9719,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9775,7 +9775,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>4.198911195753388</v>
@@ -9798,7 +9798,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9821,7 +9821,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9844,7 +9844,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9867,7 +9867,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9923,7 +9923,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>4.198911195753388</v>
@@ -9946,7 +9946,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9969,7 +9969,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9992,7 +9992,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10015,7 +10015,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10071,7 +10071,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.012913138782225</v>
@@ -10094,7 +10094,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -10117,7 +10117,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -10140,7 +10140,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10163,7 +10163,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10219,7 +10219,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.012913138782225</v>
@@ -10242,7 +10242,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -10265,7 +10265,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -10288,7 +10288,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10311,7 +10311,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10403,7 +10403,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -10462,7 +10462,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -10521,7 +10521,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -10580,7 +10580,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10639,7 +10639,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>

--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/3_five_bus_radial_grid_1ph_dyn_MP_pf_sc_results_0_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/3_five_bus_radial_grid_1ph_dyn_MP_pf_sc_results_0_bus.xlsx
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>84.28940677566904</v>
+        <v>84.28940677566905</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -734,13 +734,13 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632981</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474104424</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
         <v>13.24394453563996</v>
@@ -752,10 +752,10 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.9526279647833884</v>
+        <v>0.9526279647833883</v>
       </c>
       <c r="Q2">
-        <v>-8.694545057164095E-11</v>
+        <v>-8.693354008495316E-11</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9526279646671958</v>
+        <v>0.952627964667196</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -814,7 +814,7 @@
         <v>0.9526279648965611</v>
       </c>
       <c r="Q3">
-        <v>1.457191851518322E-10</v>
+        <v>1.457663095052449E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -864,22 +864,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9526279646404244</v>
+        <v>0.9526279646404248</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9526279649233326</v>
+        <v>0.9526279649233322</v>
       </c>
       <c r="Q4">
-        <v>1.564839686934894E-09</v>
+        <v>1.564899916669544E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999984264</v>
+        <v>179.9999999984265</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -923,22 +923,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5500000113265527</v>
+        <v>0.9526279644483024</v>
       </c>
       <c r="O5">
-        <v>0.5500000124822034</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.100000023808756</v>
+        <v>0.9526279651154547</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999918184</v>
+        <v>2.726243275115589E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999918195</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>5.341946361512345E-13</v>
+        <v>179.9999999972651</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -982,22 +982,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5500000113265525</v>
+        <v>0.9526279644483026</v>
       </c>
       <c r="O6">
-        <v>0.5500000124822035</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.100000023808756</v>
+        <v>0.9526279651154546</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999918184</v>
+        <v>2.726239814505391E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999918194</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>5.208397702474536E-13</v>
+        <v>179.9999999972651</v>
       </c>
     </row>
   </sheetData>
@@ -1098,7 +1098,7 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632981</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
@@ -1119,7 +1119,7 @@
         <v>0.8960735769153692</v>
       </c>
       <c r="Q2">
-        <v>5.76620988499712</v>
+        <v>5.766209884997119</v>
       </c>
       <c r="R2">
         <v>-121.3466079962484</v>
@@ -1172,19 +1172,19 @@
         <v>1.02022644131502</v>
       </c>
       <c r="O3">
-        <v>0.2400406981630182</v>
+        <v>0.2400406981630186</v>
       </c>
       <c r="P3">
         <v>0.8960735770061726</v>
       </c>
       <c r="Q3">
-        <v>5.766209884977154</v>
+        <v>5.766209884977161</v>
       </c>
       <c r="R3">
         <v>-121.3466079609365</v>
       </c>
       <c r="S3">
-        <v>173.4315681785684</v>
+        <v>173.4315681785683</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1231,19 +1231,19 @@
         <v>1.020226441292307</v>
       </c>
       <c r="O4">
-        <v>0.2400406981651689</v>
+        <v>0.2400406981651692</v>
       </c>
       <c r="P4">
-        <v>0.8960735770323208</v>
+        <v>0.8960735770323209</v>
       </c>
       <c r="Q4">
-        <v>5.766209886018044</v>
+        <v>5.766209886018045</v>
       </c>
       <c r="R4">
         <v>-121.346607946951</v>
       </c>
       <c r="S4">
-        <v>173.4315681777209</v>
+        <v>173.4315681777208</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1287,22 +1287,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6816683455742607</v>
+        <v>1.020226441141183</v>
       </c>
       <c r="O5">
-        <v>0.4761907158671909</v>
+        <v>0.2400406979978036</v>
       </c>
       <c r="P5">
-        <v>1.100000023812009</v>
+        <v>0.8960735771819658</v>
       </c>
       <c r="Q5">
-        <v>-164.9034422503123</v>
+        <v>5.766209886546441</v>
       </c>
       <c r="R5">
-        <v>158.1097491771482</v>
+        <v>-121.3466078867097</v>
       </c>
       <c r="S5">
-        <v>8.012919542244824E-14</v>
+        <v>173.4315681791973</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1346,22 +1346,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6816683455742606</v>
+        <v>1.020226441141183</v>
       </c>
       <c r="O6">
-        <v>0.476190715867191</v>
+        <v>0.2400406979978036</v>
       </c>
       <c r="P6">
-        <v>1.100000023812009</v>
+        <v>0.8960735771819658</v>
       </c>
       <c r="Q6">
-        <v>-164.9034422503123</v>
+        <v>5.766209886546441</v>
       </c>
       <c r="R6">
-        <v>158.1097491771482</v>
+        <v>-121.3466078867097</v>
       </c>
       <c r="S6">
-        <v>7.178240423260987E-14</v>
+        <v>173.4315681791973</v>
       </c>
     </row>
   </sheetData>
@@ -1462,13 +1462,13 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632981</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474104424</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
         <v>13.24394453563996</v>
@@ -1483,7 +1483,7 @@
         <v>0.8960735769153692</v>
       </c>
       <c r="Q2">
-        <v>5.766209884997121</v>
+        <v>5.766209884997127</v>
       </c>
       <c r="R2">
         <v>-121.3466079962484</v>
@@ -1536,13 +1536,13 @@
         <v>1.02022644131502</v>
       </c>
       <c r="O3">
-        <v>0.2400406981630181</v>
+        <v>0.2400406981630188</v>
       </c>
       <c r="P3">
-        <v>0.8960735770061727</v>
+        <v>0.8960735770061726</v>
       </c>
       <c r="Q3">
-        <v>5.766209884977162</v>
+        <v>5.766209884977206</v>
       </c>
       <c r="R3">
         <v>-121.3466079609364</v>
@@ -1595,13 +1595,13 @@
         <v>1.020226441292307</v>
       </c>
       <c r="O4">
-        <v>0.2400406981651688</v>
+        <v>0.2400406981651694</v>
       </c>
       <c r="P4">
-        <v>0.896073577032321</v>
+        <v>0.8960735770323209</v>
       </c>
       <c r="Q4">
-        <v>5.766209886018055</v>
+        <v>5.766209886018093</v>
       </c>
       <c r="R4">
         <v>-121.3466079469509</v>
@@ -1651,22 +1651,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6816683455620866</v>
+        <v>1.020226441133987</v>
       </c>
       <c r="O5">
-        <v>0.4761907158785918</v>
+        <v>0.240040697989834</v>
       </c>
       <c r="P5">
-        <v>1.100000023812009</v>
+        <v>0.8960735771890919</v>
       </c>
       <c r="Q5">
-        <v>-164.9034422500781</v>
+        <v>5.766209886571655</v>
       </c>
       <c r="R5">
-        <v>158.1097491777616</v>
+        <v>-121.346607883841</v>
       </c>
       <c r="S5">
-        <v>9.014534485025426E-14</v>
+        <v>173.4315681792677</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1710,22 +1710,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6816683455620866</v>
+        <v>1.020226441133987</v>
       </c>
       <c r="O6">
-        <v>0.4761907158785918</v>
+        <v>0.2400406979898341</v>
       </c>
       <c r="P6">
-        <v>1.100000023812008</v>
+        <v>0.8960735771890919</v>
       </c>
       <c r="Q6">
-        <v>-164.903442250078</v>
+        <v>5.766209886571657</v>
       </c>
       <c r="R6">
-        <v>158.1097491777616</v>
+        <v>-121.346607883841</v>
       </c>
       <c r="S6">
-        <v>8.847598661228661E-14</v>
+        <v>173.4315681792677</v>
       </c>
     </row>
   </sheetData>
@@ -1805,28 +1805,28 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.636363763754282</v>
+        <v>3.63636376375428</v>
       </c>
       <c r="D2">
-        <v>3.636363763754282</v>
+        <v>3.63636376375428</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>230.9401157662429</v>
+        <v>230.9401157662428</v>
       </c>
       <c r="G2">
-        <v>230.9401157662429</v>
+        <v>230.9401157662428</v>
       </c>
       <c r="H2">
-        <v>1.504993724976268</v>
+        <v>1.504993724976269</v>
       </c>
       <c r="I2">
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671081</v>
+        <v>1.50499372167108</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -1838,22 +1838,22 @@
         <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.8660254037845061</v>
+        <v>0.8660254037845059</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.86602540378499</v>
+        <v>0.8660254037849899</v>
       </c>
       <c r="Q2">
-        <v>1.71991883504212E-10</v>
+        <v>1.720024460602975E-10</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9999999998194</v>
+        <v>179.9999999998193</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1903,16 +1903,16 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.8660254038905285</v>
+        <v>0.8660254038905283</v>
       </c>
       <c r="Q3">
-        <v>4.106938631017812E-10</v>
+        <v>4.106906290937637E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999995807</v>
+        <v>179.9999999995806</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1962,10 +1962,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.866025403914866</v>
+        <v>0.8660254039148657</v>
       </c>
       <c r="Q4">
-        <v>3.135411546893584E-09</v>
+        <v>3.135399635865792E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2015,22 +2015,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4999999994714411</v>
+        <v>0.8660254034795124</v>
       </c>
       <c r="O5">
-        <v>0.5000000005289075</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.000000000000349</v>
+        <v>0.8660254040899834</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999870975</v>
+        <v>4.299793892562619E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999870986</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>5.582334068604297E-13</v>
+        <v>179.9999999956915</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2074,22 +2074,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4999999994714412</v>
+        <v>0.8660254034795124</v>
       </c>
       <c r="O6">
-        <v>0.5000000005289077</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.000000000000349</v>
+        <v>0.8660254040899834</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999870976</v>
+        <v>4.299803162428938E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999870986</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>5.582334068604295E-13</v>
+        <v>179.9999999956915</v>
       </c>
     </row>
   </sheetData>
@@ -2169,28 +2169,28 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.636363763754282</v>
+        <v>3.63636376375428</v>
       </c>
       <c r="D2">
-        <v>3.636363763754282</v>
+        <v>3.63636376375428</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>230.9401157662429</v>
+        <v>230.9401157662428</v>
       </c>
       <c r="G2">
-        <v>230.9401157662429</v>
+        <v>230.9401157662428</v>
       </c>
       <c r="H2">
-        <v>1.504993724976268</v>
+        <v>1.504993724976269</v>
       </c>
       <c r="I2">
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671081</v>
+        <v>1.50499372167108</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -2202,22 +2202,22 @@
         <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.8660254037845061</v>
+        <v>0.8660254037845059</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.86602540378499</v>
+        <v>0.8660254037849899</v>
       </c>
       <c r="Q2">
-        <v>1.71991883504212E-10</v>
+        <v>1.720024460602975E-10</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9999999998194</v>
+        <v>179.9999999998193</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2267,16 +2267,16 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.8660254038905285</v>
+        <v>0.8660254038905283</v>
       </c>
       <c r="Q3">
-        <v>4.106938631017812E-10</v>
+        <v>4.106906290937637E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999995807</v>
+        <v>179.9999999995806</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2326,10 +2326,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.866025403914866</v>
+        <v>0.8660254039148657</v>
       </c>
       <c r="Q4">
-        <v>3.135411546893584E-09</v>
+        <v>3.135399635865792E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2379,22 +2379,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4999999994714411</v>
+        <v>0.8660254034795124</v>
       </c>
       <c r="O5">
-        <v>0.5000000005289075</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.000000000000349</v>
+        <v>0.8660254040899834</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999870975</v>
+        <v>4.299793892562619E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999870986</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>5.582334068604297E-13</v>
+        <v>179.9999999956915</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2438,22 +2438,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4999999994714412</v>
+        <v>0.8660254034795124</v>
       </c>
       <c r="O6">
-        <v>0.5000000005289077</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.000000000000349</v>
+        <v>0.8660254040899834</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999870976</v>
+        <v>4.299803162428938E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999870986</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>5.582334068604295E-13</v>
+        <v>179.9999999956915</v>
       </c>
     </row>
   </sheetData>
@@ -2548,13 +2548,13 @@
         <v>194.0417843782413</v>
       </c>
       <c r="H2">
-        <v>1.504993724976268</v>
+        <v>1.504993724976269</v>
       </c>
       <c r="I2">
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671081</v>
+        <v>1.50499372167108</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -2569,13 +2569,13 @@
         <v>0.9220324944339027</v>
       </c>
       <c r="O2">
-        <v>0.1964063473242865</v>
+        <v>0.1964063473242864</v>
       </c>
       <c r="P2">
         <v>0.8180121061818276</v>
       </c>
       <c r="Q2">
-        <v>5.173976904115783</v>
+        <v>5.173976904115774</v>
       </c>
       <c r="R2">
         <v>-122.1449202961592</v>
@@ -2625,19 +2625,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9220324943451751</v>
+        <v>0.922032494345175</v>
       </c>
       <c r="O3">
         <v>0.1964063472166726</v>
       </c>
       <c r="P3">
-        <v>0.8180121062689195</v>
+        <v>0.8180121062689192</v>
       </c>
       <c r="Q3">
-        <v>5.173976904114569</v>
+        <v>5.173976904114554</v>
       </c>
       <c r="R3">
-        <v>-122.1449202549968</v>
+        <v>-122.1449202549969</v>
       </c>
       <c r="S3">
         <v>174.1659345864976</v>
@@ -2687,16 +2687,16 @@
         <v>0.9220324943235482</v>
       </c>
       <c r="O4">
-        <v>0.1964063472443384</v>
+        <v>0.1964063472443383</v>
       </c>
       <c r="P4">
-        <v>0.8180121062966177</v>
+        <v>0.8180121062966172</v>
       </c>
       <c r="Q4">
-        <v>5.173976906219916</v>
+        <v>5.173976906219901</v>
       </c>
       <c r="R4">
-        <v>-122.1449202329782</v>
+        <v>-122.1449202329783</v>
       </c>
       <c r="S4">
         <v>174.1659345844574</v>
@@ -2743,22 +2743,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6078088901105027</v>
+        <v>0.9220324941759883</v>
       </c>
       <c r="O5">
-        <v>0.4340870107119882</v>
+        <v>0.1964063470808814</v>
       </c>
       <c r="P5">
-        <v>1.000000000005794</v>
+        <v>0.818012106443318</v>
       </c>
       <c r="Q5">
-        <v>-166.2935793191085</v>
+        <v>5.173976906823892</v>
       </c>
       <c r="R5">
-        <v>160.6235536416968</v>
+        <v>-122.1449201610732</v>
       </c>
       <c r="S5">
-        <v>1.322131753083292E-13</v>
+        <v>174.1659345857627</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2802,22 +2802,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6078088901105027</v>
+        <v>0.9220324941759882</v>
       </c>
       <c r="O6">
-        <v>0.4340870107119884</v>
+        <v>0.1964063470808815</v>
       </c>
       <c r="P6">
-        <v>1.000000000005794</v>
+        <v>0.818012106443318</v>
       </c>
       <c r="Q6">
-        <v>-166.2935793191085</v>
+        <v>5.173976906823897</v>
       </c>
       <c r="R6">
-        <v>160.6235536416968</v>
+        <v>-122.1449201610732</v>
       </c>
       <c r="S6">
-        <v>1.340494694098338E-13</v>
+        <v>174.1659345857627</v>
       </c>
     </row>
   </sheetData>
@@ -2912,13 +2912,13 @@
         <v>194.0417843782413</v>
       </c>
       <c r="H2">
-        <v>1.504993724976268</v>
+        <v>1.504993724976269</v>
       </c>
       <c r="I2">
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671081</v>
+        <v>1.50499372167108</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -2933,13 +2933,13 @@
         <v>0.9220324944339027</v>
       </c>
       <c r="O2">
-        <v>0.1964063473242865</v>
+        <v>0.1964063473242864</v>
       </c>
       <c r="P2">
         <v>0.8180121061818276</v>
       </c>
       <c r="Q2">
-        <v>5.173976904115783</v>
+        <v>5.173976904115774</v>
       </c>
       <c r="R2">
         <v>-122.1449202961592</v>
@@ -2989,19 +2989,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9220324943451751</v>
+        <v>0.922032494345175</v>
       </c>
       <c r="O3">
         <v>0.1964063472166726</v>
       </c>
       <c r="P3">
-        <v>0.8180121062689195</v>
+        <v>0.8180121062689192</v>
       </c>
       <c r="Q3">
-        <v>5.173976904114569</v>
+        <v>5.173976904114554</v>
       </c>
       <c r="R3">
-        <v>-122.1449202549968</v>
+        <v>-122.1449202549969</v>
       </c>
       <c r="S3">
         <v>174.1659345864976</v>
@@ -3051,16 +3051,16 @@
         <v>0.9220324943235482</v>
       </c>
       <c r="O4">
-        <v>0.1964063472443384</v>
+        <v>0.1964063472443383</v>
       </c>
       <c r="P4">
-        <v>0.8180121062966177</v>
+        <v>0.8180121062966172</v>
       </c>
       <c r="Q4">
-        <v>5.173976906219916</v>
+        <v>5.173976906219901</v>
       </c>
       <c r="R4">
-        <v>-122.1449202329782</v>
+        <v>-122.1449202329783</v>
       </c>
       <c r="S4">
         <v>174.1659345844574</v>
@@ -3107,22 +3107,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6078088901105027</v>
+        <v>0.9220324941759883</v>
       </c>
       <c r="O5">
-        <v>0.4340870107119882</v>
+        <v>0.1964063470808814</v>
       </c>
       <c r="P5">
-        <v>1.000000000005794</v>
+        <v>0.818012106443318</v>
       </c>
       <c r="Q5">
-        <v>-166.2935793191085</v>
+        <v>5.173976906823892</v>
       </c>
       <c r="R5">
-        <v>160.6235536416968</v>
+        <v>-122.1449201610732</v>
       </c>
       <c r="S5">
-        <v>1.322131753083292E-13</v>
+        <v>174.1659345857627</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3166,22 +3166,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6078088901105027</v>
+        <v>0.9220324941759882</v>
       </c>
       <c r="O6">
-        <v>0.4340870107119884</v>
+        <v>0.1964063470808815</v>
       </c>
       <c r="P6">
-        <v>1.000000000005794</v>
+        <v>0.818012106443318</v>
       </c>
       <c r="Q6">
-        <v>-166.2935793191085</v>
+        <v>5.173976906823897</v>
       </c>
       <c r="R6">
-        <v>160.6235536416968</v>
+        <v>-122.1449201610732</v>
       </c>
       <c r="S6">
-        <v>1.340494694098338E-13</v>
+        <v>174.1659345857627</v>
       </c>
     </row>
   </sheetData>
@@ -3285,7 +3285,7 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632981</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
@@ -3297,16 +3297,16 @@
         <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.6350853098740156</v>
+        <v>0.6350853098740157</v>
       </c>
       <c r="O2">
         <v>1.100000023884844</v>
       </c>
       <c r="P2">
-        <v>0.6350853099409385</v>
+        <v>0.6350853099409386</v>
       </c>
       <c r="Q2">
-        <v>59.99999999685334</v>
+        <v>59.99999999685333</v>
       </c>
       <c r="R2">
         <v>-89.99999999999635</v>
@@ -3359,19 +3359,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6350853099894119</v>
+        <v>0.635085309989412</v>
       </c>
       <c r="O3">
         <v>1.100000023884844</v>
       </c>
       <c r="P3">
-        <v>0.6350853098300098</v>
+        <v>0.63508530983001</v>
       </c>
       <c r="Q3">
         <v>60.00000000239911</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999584</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S3">
         <v>120.0000000058974</v>
@@ -3421,22 +3421,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6350853100298056</v>
+        <v>0.6350853100298059</v>
       </c>
       <c r="O4">
         <v>1.100000023884844</v>
       </c>
       <c r="P4">
-        <v>0.635085309816861</v>
+        <v>0.6350853098168614</v>
       </c>
       <c r="Q4">
-        <v>60.00000000166487</v>
+        <v>60.00000000166484</v>
       </c>
       <c r="R4">
         <v>-89.99999999999582</v>
       </c>
       <c r="S4">
-        <v>120.0000000094205</v>
+        <v>120.0000000094206</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3483,22 +3483,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.970108835319051</v>
+        <v>0.6350853102238365</v>
       </c>
       <c r="O5">
-        <v>0.9701088349395171</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P5">
-        <v>0.366666674710274</v>
+        <v>0.6350853096441132</v>
       </c>
       <c r="Q5">
-        <v>-100.893394649348</v>
+        <v>60.00000000955424</v>
       </c>
       <c r="R5">
-        <v>100.8933946536594</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S5">
-        <v>6.039343466929195E-08</v>
+        <v>120.0000000206356</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3545,22 +3545,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.970108835319051</v>
+        <v>0.6350853102238365</v>
       </c>
       <c r="O6">
-        <v>0.9701088349395171</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P6">
-        <v>0.3666666747102741</v>
+        <v>0.6350853096441131</v>
       </c>
       <c r="Q6">
-        <v>-100.893394649348</v>
+        <v>60.00000000955424</v>
       </c>
       <c r="R6">
-        <v>100.8933946536594</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S6">
-        <v>6.039342465314252E-08</v>
+        <v>120.0000000206356</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -3667,19 +3667,19 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632981</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474104424</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
         <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.6350853098740157</v>
+        <v>0.6350853098740156</v>
       </c>
       <c r="O2">
         <v>1.100000023884844</v>
@@ -3688,7 +3688,7 @@
         <v>0.6350853099409385</v>
       </c>
       <c r="Q2">
-        <v>59.99999999685333</v>
+        <v>59.99999999685334</v>
       </c>
       <c r="R2">
         <v>-89.99999999999635</v>
@@ -3747,13 +3747,13 @@
         <v>1.100000023884844</v>
       </c>
       <c r="P3">
-        <v>0.63508530983001</v>
+        <v>0.6350853098300098</v>
       </c>
       <c r="Q3">
         <v>60.00000000239911</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999582</v>
+        <v>-89.99999999999584</v>
       </c>
       <c r="S3">
         <v>120.0000000058974</v>
@@ -3803,22 +3803,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6350853100298055</v>
+        <v>0.6350853100298054</v>
       </c>
       <c r="O4">
         <v>1.100000023884844</v>
       </c>
       <c r="P4">
-        <v>0.6350853098168613</v>
+        <v>0.6350853098168611</v>
       </c>
       <c r="Q4">
-        <v>60.00000000166486</v>
+        <v>60.00000000166484</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999582</v>
+        <v>-89.99999999999584</v>
       </c>
       <c r="S4">
-        <v>120.0000000094206</v>
+        <v>120.0000000094205</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3865,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9701088353248785</v>
+        <v>0.6350853102330758</v>
       </c>
       <c r="O5">
-        <v>0.9701088349339109</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P5">
-        <v>0.3666666747114447</v>
+        <v>0.6350853096358868</v>
       </c>
       <c r="Q5">
-        <v>-100.893394649317</v>
+        <v>60.00000000992994</v>
       </c>
       <c r="R5">
-        <v>100.8933946537583</v>
+        <v>-89.99999999999584</v>
       </c>
       <c r="S5">
-        <v>6.221287822827637E-08</v>
+        <v>120.0000000211696</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3927,22 +3927,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9701088353248783</v>
+        <v>0.6350853102330758</v>
       </c>
       <c r="O6">
-        <v>0.9701088349339106</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P6">
-        <v>0.3666666747114447</v>
+        <v>0.6350853096358868</v>
       </c>
       <c r="Q6">
-        <v>-100.893394649317</v>
+        <v>60.00000000992994</v>
       </c>
       <c r="R6">
-        <v>100.8933946537583</v>
+        <v>-89.99999999999584</v>
       </c>
       <c r="S6">
-        <v>6.221289826057524E-08</v>
+        <v>120.0000000211696</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4049,7 +4049,7 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632981</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
@@ -4061,7 +4061,7 @@
         <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.6918398877278029</v>
+        <v>0.6918398877278028</v>
       </c>
       <c r="O2">
         <v>1.100000023874158</v>
@@ -4070,10 +4070,10 @@
         <v>0.8378427578966809</v>
       </c>
       <c r="Q2">
-        <v>40.40951795604943</v>
+        <v>40.40951795604942</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999652</v>
       </c>
       <c r="S2">
         <v>128.9574716956184</v>
@@ -4129,16 +4129,16 @@
         <v>1.100000023874165</v>
       </c>
       <c r="P3">
-        <v>0.8378427578167501</v>
+        <v>0.8378427578167503</v>
       </c>
       <c r="Q3">
         <v>40.40951796258038</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999616</v>
+        <v>-89.99999999999615</v>
       </c>
       <c r="S3">
-        <v>128.9574716984651</v>
+        <v>128.9574716984652</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4185,19 +4185,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6918398877978508</v>
+        <v>0.6918398877978509</v>
       </c>
       <c r="O4">
         <v>1.100000023874165</v>
       </c>
       <c r="P4">
-        <v>0.8378427578056247</v>
+        <v>0.837842757805625</v>
       </c>
       <c r="Q4">
-        <v>40.40951796344661</v>
+        <v>40.4095179634466</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999616</v>
+        <v>-89.99999999999615</v>
       </c>
       <c r="S4">
         <v>128.9574717002523</v>
@@ -4247,22 +4247,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9443347710364155</v>
+        <v>0.6918398878771929</v>
       </c>
       <c r="O5">
-        <v>1.05598589759888</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P5">
-        <v>0.6194744497252984</v>
+        <v>0.8378427576802562</v>
       </c>
       <c r="Q5">
-        <v>-108.7881138020852</v>
+        <v>40.40951797366598</v>
       </c>
       <c r="R5">
-        <v>106.7392371182271</v>
+        <v>-89.99999999999615</v>
       </c>
       <c r="S5">
-        <v>-10.90775016075238</v>
+        <v>128.9574717054626</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4309,22 +4309,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9443347710364155</v>
+        <v>0.6918398878771927</v>
       </c>
       <c r="O6">
-        <v>1.05598589759888</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P6">
-        <v>0.6194744497252986</v>
+        <v>0.8378427576802562</v>
       </c>
       <c r="Q6">
-        <v>-108.7881138020852</v>
+        <v>40.40951797366598</v>
       </c>
       <c r="R6">
-        <v>106.7392371182271</v>
+        <v>-89.99999999999615</v>
       </c>
       <c r="S6">
-        <v>-10.90775016075238</v>
+        <v>128.9574717054626</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4374,7 +4374,7 @@
         <v>1000.000056712887</v>
       </c>
       <c r="D2">
-        <v>1.324394473835046</v>
+        <v>1.324394473835045</v>
       </c>
       <c r="E2">
         <v>13.24394453564036</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>84.28940677566904</v>
+        <v>84.28940677566905</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4579,19 +4579,19 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632981</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474104424</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
         <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.6918398877278029</v>
+        <v>0.6918398877278028</v>
       </c>
       <c r="O2">
         <v>1.100000023874158</v>
@@ -4603,7 +4603,7 @@
         <v>40.40951795604943</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999652</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S2">
         <v>128.9574716956184</v>
@@ -4659,16 +4659,16 @@
         <v>1.100000023874165</v>
       </c>
       <c r="P3">
-        <v>0.8378427578167502</v>
+        <v>0.8378427578167501</v>
       </c>
       <c r="Q3">
         <v>40.40951796258038</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999615</v>
+        <v>-89.99999999999616</v>
       </c>
       <c r="S3">
-        <v>128.9574716984652</v>
+        <v>128.9574716984651</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4715,19 +4715,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6918398877978507</v>
+        <v>0.6918398877978506</v>
       </c>
       <c r="O4">
         <v>1.100000023874165</v>
       </c>
       <c r="P4">
-        <v>0.837842757805625</v>
+        <v>0.8378427578056247</v>
       </c>
       <c r="Q4">
         <v>40.4095179634466</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999615</v>
+        <v>-89.99999999999616</v>
       </c>
       <c r="S4">
         <v>128.9574717002523</v>
@@ -4777,22 +4777,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9443347710400261</v>
+        <v>0.6918398878809706</v>
       </c>
       <c r="O5">
-        <v>1.055985897594897</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P5">
-        <v>0.6194744497227287</v>
+        <v>0.837842757674286</v>
       </c>
       <c r="Q5">
-        <v>-108.7881138019762</v>
+        <v>40.40951797415263</v>
       </c>
       <c r="R5">
-        <v>106.7392371182616</v>
+        <v>-89.99999999999616</v>
       </c>
       <c r="S5">
-        <v>-10.90775016004516</v>
+        <v>128.9574717057106</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4839,22 +4839,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9443347710400261</v>
+        <v>0.6918398878809707</v>
       </c>
       <c r="O6">
-        <v>1.055985897594897</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P6">
-        <v>0.6194744497227287</v>
+        <v>0.8378427576742858</v>
       </c>
       <c r="Q6">
-        <v>-108.7881138019762</v>
+        <v>40.40951797415263</v>
       </c>
       <c r="R6">
-        <v>106.7392371182616</v>
+        <v>-89.99999999999616</v>
       </c>
       <c r="S6">
-        <v>-10.90775016004516</v>
+        <v>128.9574717057106</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4955,13 +4955,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.504993724976268</v>
+        <v>1.504993724976269</v>
       </c>
       <c r="I2">
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671081</v>
+        <v>1.50499372167108</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -4979,7 +4979,7 @@
         <v>0.9999999999962956</v>
       </c>
       <c r="P2">
-        <v>0.5773502692541782</v>
+        <v>0.5773502692541784</v>
       </c>
       <c r="Q2">
         <v>59.99999999647621</v>
@@ -5035,16 +5035,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.577350269223176</v>
+        <v>0.5773502692231761</v>
       </c>
       <c r="O3">
         <v>0.9999999999962956</v>
       </c>
       <c r="P3">
-        <v>0.5773502691507322</v>
+        <v>0.5773502691507323</v>
       </c>
       <c r="Q3">
-        <v>60.00000000216506</v>
+        <v>60.00000000216505</v>
       </c>
       <c r="R3">
         <v>-89.99999999999582</v>
@@ -5103,16 +5103,16 @@
         <v>0.9999999999962956</v>
       </c>
       <c r="P4">
-        <v>0.5773502691501724</v>
+        <v>0.5773502691501725</v>
       </c>
       <c r="Q4">
-        <v>59.99999999947243</v>
+        <v>59.9999999994724</v>
       </c>
       <c r="R4">
         <v>-89.99999999999582</v>
       </c>
       <c r="S4">
-        <v>120.000000007461</v>
+        <v>120.0000000074609</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5159,22 +5159,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.881917103846583</v>
+        <v>0.5773502694565702</v>
       </c>
       <c r="O5">
-        <v>0.8819171035379949</v>
+        <v>0.9999999999962956</v>
       </c>
       <c r="P5">
-        <v>0.3333333334093272</v>
+        <v>0.5773502689852161</v>
       </c>
       <c r="Q5">
-        <v>-100.8933946496616</v>
+        <v>60.00000000775931</v>
       </c>
       <c r="R5">
-        <v>100.8933946535174</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S5">
-        <v>5.401448080610954E-08</v>
+        <v>120.0000000192411</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5221,22 +5221,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.881917103846583</v>
+        <v>0.5773502694565702</v>
       </c>
       <c r="O6">
-        <v>0.8819171035379949</v>
+        <v>0.9999999999962956</v>
       </c>
       <c r="P6">
-        <v>0.3333333334093275</v>
+        <v>0.5773502689852161</v>
       </c>
       <c r="Q6">
-        <v>-100.8933946496616</v>
+        <v>60.00000000775931</v>
       </c>
       <c r="R6">
-        <v>100.8933946535174</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S6">
-        <v>5.401445877058029E-08</v>
+        <v>120.0000000192411</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5337,13 +5337,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.504993724976268</v>
+        <v>1.504993724976269</v>
       </c>
       <c r="I2">
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671081</v>
+        <v>1.50499372167108</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -5361,7 +5361,7 @@
         <v>0.9999999999962956</v>
       </c>
       <c r="P2">
-        <v>0.5773502692541782</v>
+        <v>0.5773502692541784</v>
       </c>
       <c r="Q2">
         <v>59.99999999647621</v>
@@ -5417,16 +5417,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.577350269223176</v>
+        <v>0.5773502692231761</v>
       </c>
       <c r="O3">
         <v>0.9999999999962956</v>
       </c>
       <c r="P3">
-        <v>0.5773502691507322</v>
+        <v>0.5773502691507323</v>
       </c>
       <c r="Q3">
-        <v>60.00000000216506</v>
+        <v>60.00000000216505</v>
       </c>
       <c r="R3">
         <v>-89.99999999999582</v>
@@ -5485,16 +5485,16 @@
         <v>0.9999999999962956</v>
       </c>
       <c r="P4">
-        <v>0.5773502691501724</v>
+        <v>0.5773502691501725</v>
       </c>
       <c r="Q4">
-        <v>59.99999999947243</v>
+        <v>59.9999999994724</v>
       </c>
       <c r="R4">
         <v>-89.99999999999582</v>
       </c>
       <c r="S4">
-        <v>120.000000007461</v>
+        <v>120.0000000074609</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5541,22 +5541,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.881917103846583</v>
+        <v>0.5773502694565702</v>
       </c>
       <c r="O5">
-        <v>0.8819171035379949</v>
+        <v>0.9999999999962956</v>
       </c>
       <c r="P5">
-        <v>0.3333333334093272</v>
+        <v>0.5773502689852161</v>
       </c>
       <c r="Q5">
-        <v>-100.8933946496616</v>
+        <v>60.00000000775931</v>
       </c>
       <c r="R5">
-        <v>100.8933946535174</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S5">
-        <v>5.401448080610954E-08</v>
+        <v>120.0000000192411</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5603,22 +5603,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.881917103846583</v>
+        <v>0.5773502694565702</v>
       </c>
       <c r="O6">
-        <v>0.8819171035379949</v>
+        <v>0.9999999999962956</v>
       </c>
       <c r="P6">
-        <v>0.3333333334093275</v>
+        <v>0.5773502689852161</v>
       </c>
       <c r="Q6">
-        <v>-100.8933946496616</v>
+        <v>60.00000000775931</v>
       </c>
       <c r="R6">
-        <v>100.8933946535174</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S6">
-        <v>5.401445877058029E-08</v>
+        <v>120.0000000192411</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5719,13 +5719,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.504993724976268</v>
+        <v>1.504993724976269</v>
       </c>
       <c r="I2">
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671081</v>
+        <v>1.50499372167108</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -5808,7 +5808,7 @@
         <v>0.7472997526577979</v>
       </c>
       <c r="Q3">
-        <v>41.7746336381064</v>
+        <v>41.77463363810639</v>
       </c>
       <c r="R3">
         <v>-89.99999999999613</v>
@@ -5867,10 +5867,10 @@
         <v>0.9999999999908707</v>
       </c>
       <c r="P4">
-        <v>0.7472997526545251</v>
+        <v>0.7472997526545254</v>
       </c>
       <c r="Q4">
-        <v>41.77463363817501</v>
+        <v>41.774633638175</v>
       </c>
       <c r="R4">
         <v>-89.99999999999613</v>
@@ -5923,22 +5923,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8576025464121367</v>
+        <v>0.6184267551642108</v>
       </c>
       <c r="O5">
-        <v>0.9547184905727348</v>
+        <v>0.9999999999908707</v>
       </c>
       <c r="P5">
-        <v>0.5421614591269466</v>
+        <v>0.7472997525303007</v>
       </c>
       <c r="Q5">
-        <v>-108.0887396139939</v>
+        <v>41.7746336492082</v>
       </c>
       <c r="R5">
-        <v>106.1949204578978</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S5">
-        <v>-10.8027716731492</v>
+        <v>128.109158331695</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5985,22 +5985,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8576025464121366</v>
+        <v>0.6184267551642108</v>
       </c>
       <c r="O6">
-        <v>0.9547184905727351</v>
+        <v>0.999999999990871</v>
       </c>
       <c r="P6">
-        <v>0.5421614591269467</v>
+        <v>0.7472997525303007</v>
       </c>
       <c r="Q6">
-        <v>-108.0887396139939</v>
+        <v>41.77463364920821</v>
       </c>
       <c r="R6">
-        <v>106.1949204578978</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S6">
-        <v>-10.80277167314921</v>
+        <v>128.109158331695</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6101,13 +6101,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.504993724976268</v>
+        <v>1.504993724976269</v>
       </c>
       <c r="I2">
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671081</v>
+        <v>1.50499372167108</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -6190,7 +6190,7 @@
         <v>0.7472997526577979</v>
       </c>
       <c r="Q3">
-        <v>41.7746336381064</v>
+        <v>41.77463363810639</v>
       </c>
       <c r="R3">
         <v>-89.99999999999613</v>
@@ -6249,10 +6249,10 @@
         <v>0.9999999999908707</v>
       </c>
       <c r="P4">
-        <v>0.7472997526545251</v>
+        <v>0.7472997526545254</v>
       </c>
       <c r="Q4">
-        <v>41.77463363817501</v>
+        <v>41.774633638175</v>
       </c>
       <c r="R4">
         <v>-89.99999999999613</v>
@@ -6305,22 +6305,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8576025464121367</v>
+        <v>0.6184267551642108</v>
       </c>
       <c r="O5">
-        <v>0.9547184905727348</v>
+        <v>0.9999999999908707</v>
       </c>
       <c r="P5">
-        <v>0.5421614591269466</v>
+        <v>0.7472997525303007</v>
       </c>
       <c r="Q5">
-        <v>-108.0887396139939</v>
+        <v>41.7746336492082</v>
       </c>
       <c r="R5">
-        <v>106.1949204578978</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S5">
-        <v>-10.8027716731492</v>
+        <v>128.109158331695</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6367,22 +6367,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8576025464121366</v>
+        <v>0.6184267551642108</v>
       </c>
       <c r="O6">
-        <v>0.9547184905727351</v>
+        <v>0.999999999990871</v>
       </c>
       <c r="P6">
-        <v>0.5421614591269467</v>
+        <v>0.7472997525303007</v>
       </c>
       <c r="Q6">
-        <v>-108.0887396139939</v>
+        <v>41.77463364920821</v>
       </c>
       <c r="R6">
-        <v>106.1949204578978</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S6">
-        <v>-10.80277167314921</v>
+        <v>128.109158331695</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6489,7 +6489,7 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632981</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
@@ -6501,7 +6501,7 @@
         <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.6350853098347086</v>
+        <v>0.6350853098347083</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -6510,7 +6510,7 @@
         <v>0.6350853098507082</v>
       </c>
       <c r="Q2">
-        <v>-4.877410550668155E-09</v>
+        <v>-4.877412004532055E-09</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -6563,22 +6563,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6350853097237749</v>
+        <v>0.6350853097237747</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.6350853099661093</v>
+        <v>0.6350853099661095</v>
       </c>
       <c r="Q3">
-        <v>1.367206781682504E-09</v>
+        <v>1.367204662474348E-09</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>-179.9999999983958</v>
+        <v>-179.9999999983959</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6631,10 +6631,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.635085310006503</v>
+        <v>0.6350853100065035</v>
       </c>
       <c r="Q4">
-        <v>4.890319648218234E-09</v>
+        <v>4.890313510449186E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -6687,22 +6687,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.3666666740374639</v>
+        <v>0.6350853095378781</v>
       </c>
       <c r="O5">
-        <v>0.3666666751852969</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.7333333492227608</v>
+        <v>0.6350853102005343</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999765369</v>
+        <v>1.610535468331723E-08</v>
       </c>
       <c r="R5">
-        <v>-179.999999998587</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1.243076761049068E-08</v>
+        <v>-179.9999999912407</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6749,22 +6749,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.3666666740374638</v>
+        <v>0.6350853095378779</v>
       </c>
       <c r="O6">
-        <v>0.3666666751852971</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.7333333492227608</v>
+        <v>0.635085310200534</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999765369</v>
+        <v>1.610535905831676E-08</v>
       </c>
       <c r="R6">
-        <v>-179.999999998587</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.243075258626654E-08</v>
+        <v>-179.9999999912407</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6871,13 +6871,13 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632981</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474104424</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
         <v>13.24394453563996</v>
@@ -6892,7 +6892,7 @@
         <v>0.6350853098507082</v>
       </c>
       <c r="Q2">
-        <v>-4.877410550668154E-09</v>
+        <v>-4.877403765969959E-09</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -6945,16 +6945,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6350853097237747</v>
+        <v>0.6350853097237749</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.6350853099661096</v>
+        <v>0.6350853099661093</v>
       </c>
       <c r="Q3">
-        <v>1.367211610703726E-09</v>
+        <v>1.367279308609326E-09</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -7007,22 +7007,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.635085309710626</v>
+        <v>0.6350853097106263</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.6350853100065035</v>
+        <v>0.6350853100065034</v>
       </c>
       <c r="Q4">
-        <v>4.890332640620929E-09</v>
+        <v>4.890403457815029E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>-179.9999999991301</v>
+        <v>-179.99999999913</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7069,22 +7069,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.3666666740226305</v>
+        <v>0.6350853095296519</v>
       </c>
       <c r="O5">
-        <v>0.3666666752007156</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.733333349223346</v>
+        <v>0.6350853102097735</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999758444</v>
+        <v>1.663949337019434E-08</v>
       </c>
       <c r="R5">
-        <v>-179.9999999983697</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1.288564102058563E-08</v>
+        <v>-179.999999990865</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7131,22 +7131,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.3666666740226303</v>
+        <v>0.6350853095296521</v>
       </c>
       <c r="O6">
-        <v>0.3666666752007157</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.733333349223346</v>
+        <v>0.6350853102097735</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999758444</v>
+        <v>1.663950271619585E-08</v>
       </c>
       <c r="R6">
-        <v>-179.9999999983697</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.288563601251092E-08</v>
+        <v>-179.9999999908649</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7253,7 +7253,7 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632981</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
@@ -7268,7 +7268,7 @@
         <v>0.8378427578256962</v>
       </c>
       <c r="O2">
-        <v>0.4028253111898905</v>
+        <v>0.4028253111898906</v>
       </c>
       <c r="P2">
         <v>0.6918398877011798</v>
@@ -7277,13 +7277,13 @@
         <v>8.957471693504779</v>
       </c>
       <c r="R2">
-        <v>-115.8807585964592</v>
+        <v>-115.8807585964591</v>
       </c>
       <c r="S2">
         <v>160.4095179569557</v>
       </c>
       <c r="T2">
-        <v>3.617960382370078</v>
+        <v>3.617960382370077</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -7327,19 +7327,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8378427577457516</v>
+        <v>0.8378427577457515</v>
       </c>
       <c r="O3">
-        <v>0.4028253110952152</v>
+        <v>0.4028253110952154</v>
       </c>
       <c r="P3">
-        <v>0.6918398877448089</v>
+        <v>0.6918398877448091</v>
       </c>
       <c r="Q3">
-        <v>8.957471696351632</v>
+        <v>8.957471696351636</v>
       </c>
       <c r="R3">
-        <v>-115.8807585788046</v>
+        <v>-115.8807585788045</v>
       </c>
       <c r="S3">
         <v>160.4095179634873</v>
@@ -7398,7 +7398,7 @@
         <v>0.6918398877712165</v>
       </c>
       <c r="Q4">
-        <v>8.957471698138811</v>
+        <v>8.957471698138812</v>
       </c>
       <c r="R4">
         <v>-115.8807585718118</v>
@@ -7451,22 +7451,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6454597856902593</v>
+        <v>0.8378427576092574</v>
       </c>
       <c r="O5">
-        <v>0.4396365304272606</v>
+        <v>0.4028253109565873</v>
       </c>
       <c r="P5">
-        <v>0.856149831639989</v>
+        <v>0.6918398878505586</v>
       </c>
       <c r="Q5">
-        <v>-153.840718235564</v>
+        <v>8.95747170334902</v>
       </c>
       <c r="R5">
-        <v>128.6858355816165</v>
+        <v>-115.8807585416912</v>
       </c>
       <c r="S5">
-        <v>-3.925473809326227</v>
+        <v>160.4095179745729</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7513,22 +7513,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6454597856902593</v>
+        <v>0.8378427576092573</v>
       </c>
       <c r="O6">
-        <v>0.4396365304272606</v>
+        <v>0.4028253109565873</v>
       </c>
       <c r="P6">
-        <v>0.8561498316399888</v>
+        <v>0.6918398878505586</v>
       </c>
       <c r="Q6">
-        <v>-153.840718235564</v>
+        <v>8.957471703349022</v>
       </c>
       <c r="R6">
-        <v>128.6858355816164</v>
+        <v>-115.8807585416912</v>
       </c>
       <c r="S6">
-        <v>-3.925473809326232</v>
+        <v>160.4095179745729</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7635,13 +7635,13 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632981</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474104424</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
         <v>13.24394453563996</v>
@@ -7650,16 +7650,16 @@
         <v>0.8378427578256962</v>
       </c>
       <c r="O2">
-        <v>0.4028253111898905</v>
+        <v>0.4028253111898907</v>
       </c>
       <c r="P2">
         <v>0.6918398877011798</v>
       </c>
       <c r="Q2">
-        <v>8.957471693504779</v>
+        <v>8.957471693504795</v>
       </c>
       <c r="R2">
-        <v>-115.8807585964592</v>
+        <v>-115.8807585964591</v>
       </c>
       <c r="S2">
         <v>160.4095179569557</v>
@@ -7709,22 +7709,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8378427577457515</v>
+        <v>0.8378427577457516</v>
       </c>
       <c r="O3">
-        <v>0.402825311095215</v>
+        <v>0.4028253110952158</v>
       </c>
       <c r="P3">
-        <v>0.6918398877448091</v>
+        <v>0.6918398877448089</v>
       </c>
       <c r="Q3">
-        <v>8.957471696351631</v>
+        <v>8.957471696351679</v>
       </c>
       <c r="R3">
         <v>-115.8807585788045</v>
       </c>
       <c r="S3">
-        <v>160.4095179634874</v>
+        <v>160.4095179634873</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7771,16 +7771,16 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8378427577346261</v>
+        <v>0.8378427577346264</v>
       </c>
       <c r="O4">
-        <v>0.4028253110970195</v>
+        <v>0.4028253110970204</v>
       </c>
       <c r="P4">
-        <v>0.6918398877712169</v>
+        <v>0.6918398877712166</v>
       </c>
       <c r="Q4">
-        <v>8.957471698138811</v>
+        <v>8.95747169813886</v>
       </c>
       <c r="R4">
         <v>-115.8807585718118</v>
@@ -7833,22 +7833,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6454597856809604</v>
+        <v>0.8378427576032875</v>
       </c>
       <c r="O5">
-        <v>0.439636530430932</v>
+        <v>0.4028253109499005</v>
       </c>
       <c r="P5">
-        <v>0.8561498316391783</v>
+        <v>0.6918398878543368</v>
       </c>
       <c r="Q5">
-        <v>-153.8407182350992</v>
+        <v>8.95747170359718</v>
       </c>
       <c r="R5">
-        <v>128.6858355829224</v>
+        <v>-115.8807585402568</v>
       </c>
       <c r="S5">
-        <v>-3.925473809061812</v>
+        <v>160.4095179750596</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7895,22 +7895,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6454597856809603</v>
+        <v>0.8378427576032875</v>
       </c>
       <c r="O6">
-        <v>0.4396365304309321</v>
+        <v>0.4028253109499005</v>
       </c>
       <c r="P6">
-        <v>0.8561498316391785</v>
+        <v>0.6918398878543367</v>
       </c>
       <c r="Q6">
-        <v>-153.8407182350992</v>
+        <v>8.957471703597177</v>
       </c>
       <c r="R6">
-        <v>128.6858355829224</v>
+        <v>-115.8807585402568</v>
       </c>
       <c r="S6">
-        <v>-3.925473809061821</v>
+        <v>160.4095179750596</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>4.198911196109217</v>
+        <v>4.198911196109218</v>
       </c>
       <c r="D2">
         <v>4.198911195412808</v>
@@ -8005,19 +8005,19 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>266.6666760314689</v>
+        <v>266.666676031469</v>
       </c>
       <c r="G2">
         <v>266.666675987241</v>
       </c>
       <c r="H2">
-        <v>1.504993724976268</v>
+        <v>1.504993724976269</v>
       </c>
       <c r="I2">
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671081</v>
+        <v>1.50499372167108</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -8029,7 +8029,7 @@
         <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.5773502691952341</v>
+        <v>0.5773502691952339</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -8038,7 +8038,7 @@
         <v>0.5773502691743764</v>
       </c>
       <c r="Q2">
-        <v>-5.812891580505248E-09</v>
+        <v>-5.812895899830532E-09</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -8097,10 +8097,10 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.5773502692819934</v>
+        <v>0.5773502692819932</v>
       </c>
       <c r="Q3">
-        <v>5.928463223784435E-10</v>
+        <v>5.928320519327688E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -8159,10 +8159,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.5773502693301085</v>
+        <v>0.5773502693301082</v>
       </c>
       <c r="Q4">
-        <v>6.074341337611677E-09</v>
+        <v>6.07433219123911E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -8215,22 +8215,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.333333332841134</v>
+        <v>0.5773502689262674</v>
       </c>
       <c r="O5">
-        <v>0.3333333338615928</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.6666666667027268</v>
+        <v>0.5773502695153875</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999692109</v>
+        <v>1.785443969161503E-08</v>
       </c>
       <c r="R5">
-        <v>179.9999999919938</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1.139144862183935E-08</v>
+        <v>-179.9999999950684</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8277,22 +8277,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.3333333328411343</v>
+        <v>0.5773502689262673</v>
       </c>
       <c r="O6">
-        <v>0.3333333338615929</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.6666666667027271</v>
+        <v>0.5773502695153874</v>
       </c>
       <c r="Q6">
-        <v>-179.999999969211</v>
+        <v>1.78544532565563E-08</v>
       </c>
       <c r="R6">
-        <v>179.9999999919939</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.139144586739819E-08</v>
+        <v>-179.9999999950684</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8336,10 +8336,10 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>3.617960382498489</v>
+        <v>3.617960382498488</v>
       </c>
       <c r="C2">
-        <v>689.3140322484581</v>
+        <v>689.314032248458</v>
       </c>
       <c r="D2">
         <v>1.324394473835046</v>
@@ -8348,10 +8348,10 @@
         <v>13.24394453564036</v>
       </c>
       <c r="F2">
-        <v>0.4028253111823098</v>
+        <v>0.4028253111823096</v>
       </c>
       <c r="G2">
-        <v>45.00000000004626</v>
+        <v>45.00000000004628</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8371,10 +8371,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.4028253110876386</v>
+        <v>0.4028253110876379</v>
       </c>
       <c r="G3">
-        <v>-25.8807585799728</v>
+        <v>-25.88075857997278</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -8394,10 +8394,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.4028253110894432</v>
+        <v>0.4028253110894425</v>
       </c>
       <c r="G4">
-        <v>-25.88075857298007</v>
+        <v>-25.88075857298004</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -8417,10 +8417,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.4028253109490408</v>
+        <v>0.4028253109490099</v>
       </c>
       <c r="G5">
-        <v>-175.8807585428509</v>
+        <v>-25.8807585428594</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -8440,10 +8440,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.4028253109490408</v>
+        <v>0.4028253109490099</v>
       </c>
       <c r="G6">
-        <v>-175.8807585428509</v>
+        <v>-25.8807585428594</v>
       </c>
     </row>
   </sheetData>
@@ -8526,7 +8526,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>4.198911196109217</v>
+        <v>4.198911196109218</v>
       </c>
       <c r="D2">
         <v>4.198911195412808</v>
@@ -8535,19 +8535,19 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>266.6666760314689</v>
+        <v>266.666676031469</v>
       </c>
       <c r="G2">
         <v>266.666675987241</v>
       </c>
       <c r="H2">
-        <v>1.504993724976268</v>
+        <v>1.504993724976269</v>
       </c>
       <c r="I2">
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671081</v>
+        <v>1.50499372167108</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -8559,7 +8559,7 @@
         <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.5773502691952341</v>
+        <v>0.5773502691952339</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -8568,7 +8568,7 @@
         <v>0.5773502691743764</v>
       </c>
       <c r="Q2">
-        <v>-5.812891580505248E-09</v>
+        <v>-5.812895899830532E-09</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -8627,10 +8627,10 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.5773502692819934</v>
+        <v>0.5773502692819932</v>
       </c>
       <c r="Q3">
-        <v>5.928463223784435E-10</v>
+        <v>5.928320519327688E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -8689,10 +8689,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.5773502693301085</v>
+        <v>0.5773502693301082</v>
       </c>
       <c r="Q4">
-        <v>6.074341337611677E-09</v>
+        <v>6.07433219123911E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -8745,22 +8745,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.333333332841134</v>
+        <v>0.5773502689262674</v>
       </c>
       <c r="O5">
-        <v>0.3333333338615928</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.6666666667027268</v>
+        <v>0.5773502695153875</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999692109</v>
+        <v>1.785443969161503E-08</v>
       </c>
       <c r="R5">
-        <v>179.9999999919938</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1.139144862183935E-08</v>
+        <v>-179.9999999950684</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8807,22 +8807,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.3333333328411343</v>
+        <v>0.5773502689262673</v>
       </c>
       <c r="O6">
-        <v>0.3333333338615929</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.6666666667027271</v>
+        <v>0.5773502695153874</v>
       </c>
       <c r="Q6">
-        <v>-179.999999969211</v>
+        <v>1.78544532565563E-08</v>
       </c>
       <c r="R6">
-        <v>179.9999999919939</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.139144586739819E-08</v>
+        <v>-179.9999999950684</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8923,13 +8923,13 @@
         <v>191.3456832773375</v>
       </c>
       <c r="H2">
-        <v>1.504993724976268</v>
+        <v>1.504993724976269</v>
       </c>
       <c r="I2">
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671081</v>
+        <v>1.50499372167108</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -9012,7 +9012,7 @@
         <v>0.6184267550841061</v>
       </c>
       <c r="Q3">
-        <v>8.109158321931385</v>
+        <v>8.109158321931371</v>
       </c>
       <c r="R3">
         <v>-117.0248837562165</v>
@@ -9071,13 +9071,13 @@
         <v>0.3354590831006826</v>
       </c>
       <c r="P4">
-        <v>0.6184267551237353</v>
+        <v>0.6184267551237351</v>
       </c>
       <c r="Q4">
-        <v>8.109158324959909</v>
+        <v>8.109158324959898</v>
       </c>
       <c r="R4">
-        <v>-117.0248837452071</v>
+        <v>-117.0248837452072</v>
       </c>
       <c r="S4">
         <v>161.7746336388059</v>
@@ -9127,22 +9127,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5655462790792672</v>
+        <v>0.7472997525143641</v>
       </c>
       <c r="O5">
-        <v>0.37925891582052</v>
+        <v>0.3354590829610916</v>
       </c>
       <c r="P5">
-        <v>0.7679592756105802</v>
+        <v>0.6184267552078957</v>
       </c>
       <c r="Q5">
-        <v>-155.6266319927826</v>
+        <v>8.109158330815609</v>
       </c>
       <c r="R5">
-        <v>131.465684045736</v>
+        <v>-117.0248837092546</v>
       </c>
       <c r="S5">
-        <v>-3.793471518191368</v>
+        <v>161.7746336498391</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9189,22 +9189,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5655462790792672</v>
+        <v>0.7472997525143641</v>
       </c>
       <c r="O6">
-        <v>0.3792589158205198</v>
+        <v>0.3354590829610918</v>
       </c>
       <c r="P6">
-        <v>0.7679592756105803</v>
+        <v>0.6184267552078958</v>
       </c>
       <c r="Q6">
-        <v>-155.6266319927826</v>
+        <v>8.109158330815603</v>
       </c>
       <c r="R6">
-        <v>131.4656840457361</v>
+        <v>-117.0248837092546</v>
       </c>
       <c r="S6">
-        <v>-3.793471518191365</v>
+        <v>161.7746336498391</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9305,13 +9305,13 @@
         <v>191.3456832773375</v>
       </c>
       <c r="H2">
-        <v>1.504993724976268</v>
+        <v>1.504993724976269</v>
       </c>
       <c r="I2">
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671081</v>
+        <v>1.50499372167108</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -9394,7 +9394,7 @@
         <v>0.6184267550841061</v>
       </c>
       <c r="Q3">
-        <v>8.109158321931385</v>
+        <v>8.109158321931371</v>
       </c>
       <c r="R3">
         <v>-117.0248837562165</v>
@@ -9453,13 +9453,13 @@
         <v>0.3354590831006826</v>
       </c>
       <c r="P4">
-        <v>0.6184267551237353</v>
+        <v>0.6184267551237351</v>
       </c>
       <c r="Q4">
-        <v>8.109158324959909</v>
+        <v>8.109158324959898</v>
       </c>
       <c r="R4">
-        <v>-117.0248837452071</v>
+        <v>-117.0248837452072</v>
       </c>
       <c r="S4">
         <v>161.7746336388059</v>
@@ -9509,22 +9509,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5655462790792672</v>
+        <v>0.7472997525143641</v>
       </c>
       <c r="O5">
-        <v>0.37925891582052</v>
+        <v>0.3354590829610916</v>
       </c>
       <c r="P5">
-        <v>0.7679592756105802</v>
+        <v>0.6184267552078957</v>
       </c>
       <c r="Q5">
-        <v>-155.6266319927826</v>
+        <v>8.109158330815609</v>
       </c>
       <c r="R5">
-        <v>131.465684045736</v>
+        <v>-117.0248837092546</v>
       </c>
       <c r="S5">
-        <v>-3.793471518191368</v>
+        <v>161.7746336498391</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9571,22 +9571,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5655462790792672</v>
+        <v>0.7472997525143641</v>
       </c>
       <c r="O6">
-        <v>0.3792589158205198</v>
+        <v>0.3354590829610918</v>
       </c>
       <c r="P6">
-        <v>0.7679592756105803</v>
+        <v>0.6184267552078958</v>
       </c>
       <c r="Q6">
-        <v>-155.6266319927826</v>
+        <v>8.109158330815603</v>
       </c>
       <c r="R6">
-        <v>131.4656840457361</v>
+        <v>-117.0248837092546</v>
       </c>
       <c r="S6">
-        <v>-3.793471518191365</v>
+        <v>161.7746336498391</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9630,13 +9630,13 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>3.617960382498489</v>
+        <v>3.617960382498488</v>
       </c>
       <c r="C2">
-        <v>689.3140322484581</v>
+        <v>689.314032248458</v>
       </c>
       <c r="D2">
-        <v>1.324394473835046</v>
+        <v>1.324394473835045</v>
       </c>
       <c r="E2">
         <v>13.24394453564036</v>
@@ -9645,7 +9645,7 @@
         <v>0.4028253111823097</v>
       </c>
       <c r="G2">
-        <v>45.00000000004624</v>
+        <v>45.00000000004628</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9665,10 +9665,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.4028253110876382</v>
+        <v>0.4028253110876389</v>
       </c>
       <c r="G3">
-        <v>-25.88075857997283</v>
+        <v>-25.88075857997272</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9688,10 +9688,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.4028253110894427</v>
+        <v>0.4028253110894437</v>
       </c>
       <c r="G4">
-        <v>-25.8807585729801</v>
+        <v>-25.88075857297997</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.402825310942353</v>
+        <v>0.4028253109423239</v>
       </c>
       <c r="G5">
-        <v>-175.8807585414166</v>
+        <v>-25.88075854142503</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -9734,10 +9734,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.402825310942353</v>
+        <v>0.4028253109423238</v>
       </c>
       <c r="G6">
-        <v>-175.8807585414166</v>
+        <v>-25.88075854142505</v>
       </c>
     </row>
   </sheetData>
@@ -9784,7 +9784,7 @@
         <v>800.0000280266122</v>
       </c>
       <c r="D2">
-        <v>1.504993721305345</v>
+        <v>1.504993721305343</v>
       </c>
       <c r="E2">
         <v>15.04993697229389</v>
@@ -9932,7 +9932,7 @@
         <v>800.0000280266122</v>
       </c>
       <c r="D2">
-        <v>1.504993721305345</v>
+        <v>1.504993721305343</v>
       </c>
       <c r="E2">
         <v>15.04993697229389</v>
@@ -10080,7 +10080,7 @@
         <v>574.0370498678898</v>
       </c>
       <c r="D2">
-        <v>1.504993721305345</v>
+        <v>1.504993721305343</v>
       </c>
       <c r="E2">
         <v>15.04993697229389</v>
@@ -10089,7 +10089,7 @@
         <v>0.3354590831385725</v>
       </c>
       <c r="G2">
-        <v>44.99999999355202</v>
+        <v>44.99999999355205</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10109,10 +10109,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.335459083046671</v>
+        <v>0.3354590830466712</v>
       </c>
       <c r="G3">
-        <v>-27.0248837607183</v>
+        <v>-27.02488376071819</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10132,10 +10132,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.3354590830702972</v>
+        <v>0.3354590830702975</v>
       </c>
       <c r="G4">
-        <v>-27.02488374970902</v>
+        <v>-27.0248837497089</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10155,10 +10155,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.3354590829307358</v>
+        <v>0.3354590829307068</v>
       </c>
       <c r="G5">
-        <v>-177.0248837137474</v>
+        <v>-27.02488371375632</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10178,10 +10178,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.3354590829307358</v>
+        <v>0.3354590829307067</v>
       </c>
       <c r="G6">
-        <v>-177.0248837137474</v>
+        <v>-27.02488371375633</v>
       </c>
     </row>
   </sheetData>
@@ -10228,7 +10228,7 @@
         <v>574.0370498678898</v>
       </c>
       <c r="D2">
-        <v>1.504993721305345</v>
+        <v>1.504993721305343</v>
       </c>
       <c r="E2">
         <v>15.04993697229389</v>
@@ -10237,7 +10237,7 @@
         <v>0.3354590831385725</v>
       </c>
       <c r="G2">
-        <v>44.99999999355202</v>
+        <v>44.99999999355205</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10257,10 +10257,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.335459083046671</v>
+        <v>0.3354590830466712</v>
       </c>
       <c r="G3">
-        <v>-27.0248837607183</v>
+        <v>-27.02488376071819</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10280,10 +10280,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.3354590830702972</v>
+        <v>0.3354590830702975</v>
       </c>
       <c r="G4">
-        <v>-27.02488374970902</v>
+        <v>-27.0248837497089</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10303,10 +10303,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.3354590829307358</v>
+        <v>0.3354590829307068</v>
       </c>
       <c r="G5">
-        <v>-177.0248837137474</v>
+        <v>-27.02488371375632</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10326,10 +10326,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.3354590829307358</v>
+        <v>0.3354590829307067</v>
       </c>
       <c r="G6">
-        <v>-177.0248837137474</v>
+        <v>-27.02488371375633</v>
       </c>
     </row>
   </sheetData>
@@ -10430,7 +10430,7 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632981</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
@@ -10448,10 +10448,10 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.9526279647833884</v>
+        <v>0.9526279647833883</v>
       </c>
       <c r="Q2">
-        <v>-8.694577365250735E-11</v>
+        <v>-8.694609673337376E-11</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -10501,22 +10501,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.952627964667196</v>
+        <v>0.9526279646671958</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.9526279648965611</v>
+        <v>0.9526279648965608</v>
       </c>
       <c r="Q3">
-        <v>1.457136776604503E-10</v>
+        <v>1.457193150185654E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999998456</v>
+        <v>179.9999999998455</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -10560,16 +10560,16 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9526279646404248</v>
+        <v>0.9526279646404247</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9526279649233322</v>
+        <v>0.952627964923332</v>
       </c>
       <c r="Q4">
-        <v>1.564831887857163E-09</v>
+        <v>1.564834771078478E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -10619,22 +10619,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5500000113416789</v>
+        <v>0.9526279644570351</v>
       </c>
       <c r="O5">
-        <v>0.5500000124670774</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.100000023808756</v>
+        <v>0.9526279651067214</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999919768</v>
+        <v>2.673383005967457E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999919778</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>5.275172031993438E-13</v>
+        <v>179.9999999973179</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -10678,22 +10678,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5500000113416788</v>
+        <v>0.9526279644570351</v>
       </c>
       <c r="O6">
-        <v>0.5500000124670775</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.100000023808756</v>
+        <v>0.9526279651067214</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999919768</v>
+        <v>2.673388524993615E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999919778</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>5.241784867233986E-13</v>
+        <v>179.9999999973178</v>
       </c>
     </row>
   </sheetData>
